--- a/server/data/xlsx/MapObjectData.xlsx
+++ b/server/data/xlsx/MapObjectData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,76 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>오크 요새 던전 포탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FieldPortal</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Portal/FieldPortal_Gold</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>슬라임 평원 입구</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FieldPortal</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Portal/FieldPortal_Gold</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>고블린 습지 입구</t>
         </is>
       </c>
     </row>
